--- a/ExcelUtils/ExcelTest/Resources/.Imports/Record_Template.xlsx
+++ b/ExcelUtils/ExcelTest/Resources/.Imports/Record_Template.xlsx
@@ -279,7 +279,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,12 +342,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -485,11 +479,33 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -503,6 +519,28 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -608,7 +646,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -632,7 +670,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -644,34 +682,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,80 +721,80 @@
     <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -764,33 +802,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1355,8 +1399,8 @@
       <c r="J1" s="4"/>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:10">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -1369,48 +1413,48 @@
       <c r="J2" s="4"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:10">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:10">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="11"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="4">
